--- a/data/regional_statistics_data.xlsx
+++ b/data/regional_statistics_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E274"/>
+  <dimension ref="A1:E268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
         <v>2</v>
       </c>
       <c r="D119" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E119" t="n">
         <v>64450</v>
@@ -2970,15 +2970,19 @@
           <t>대전</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>대덕구</t>
+        </is>
+      </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D123" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>22116</v>
       </c>
     </row>
     <row r="124">
@@ -2989,17 +2993,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>대덕구</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C124" t="n">
         <v>2</v>
       </c>
       <c r="D124" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E124" t="n">
-        <v>22116</v>
+        <v>34450</v>
       </c>
     </row>
     <row r="125">
@@ -3010,17 +3014,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>서구</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D125" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="E125" t="n">
-        <v>34450</v>
+        <v>76266</v>
       </c>
     </row>
     <row r="126">
@@ -3031,17 +3035,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>서구</t>
+          <t>유성구</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D126" t="n">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="E126" t="n">
-        <v>76266</v>
+        <v>64730</v>
       </c>
     </row>
     <row r="127">
@@ -3052,38 +3056,34 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>유성구</t>
+          <t>중구</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D127" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="E127" t="n">
-        <v>64730</v>
+        <v>31457</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>대전</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>중구</t>
-        </is>
-      </c>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="E128" t="n">
-        <v>31457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3092,15 +3092,19 @@
           <t>부산</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>강서구</t>
+        </is>
+      </c>
       <c r="C129" t="n">
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>25183</v>
       </c>
     </row>
     <row r="130">
@@ -3111,17 +3115,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>강서구</t>
+          <t>금정구</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E130" t="n">
-        <v>25183</v>
+        <v>29830</v>
       </c>
     </row>
     <row r="131">
@@ -3132,17 +3136,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>금정구</t>
+          <t>기장군</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D131" t="n">
-        <v>6</v>
+        <v>116</v>
       </c>
       <c r="E131" t="n">
-        <v>29830</v>
+        <v>28602</v>
       </c>
     </row>
     <row r="132">
@@ -3153,17 +3157,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>기장군</t>
+          <t>남구</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>28602</v>
+        <v>39976</v>
       </c>
     </row>
     <row r="133">
@@ -3174,17 +3178,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>남구</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133" t="n">
-        <v>39976</v>
+        <v>7680</v>
       </c>
     </row>
     <row r="134">
@@ -3195,17 +3199,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>동래구</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D134" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E134" t="n">
-        <v>7680</v>
+        <v>39948</v>
       </c>
     </row>
     <row r="135">
@@ -3216,17 +3220,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>동래구</t>
+          <t>부산진구</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D135" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E135" t="n">
-        <v>39948</v>
+        <v>45370</v>
       </c>
     </row>
     <row r="136">
@@ -3237,17 +3241,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>부산진구</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D136" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E136" t="n">
-        <v>45370</v>
+        <v>32085</v>
       </c>
     </row>
     <row r="137">
@@ -3258,17 +3262,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>사상구</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E137" t="n">
-        <v>32085</v>
+        <v>23171</v>
       </c>
     </row>
     <row r="138">
@@ -3279,17 +3283,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>사상구</t>
+          <t>사하구</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D138" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="E138" t="n">
-        <v>23171</v>
+        <v>37062</v>
       </c>
     </row>
     <row r="139">
@@ -3300,17 +3304,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>사하구</t>
+          <t>서구</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D139" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="E139" t="n">
-        <v>37062</v>
+        <v>12336</v>
       </c>
     </row>
     <row r="140">
@@ -3321,17 +3325,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>서구</t>
+          <t>수영구</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D140" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E140" t="n">
-        <v>12336</v>
+        <v>19448</v>
       </c>
     </row>
     <row r="141">
@@ -3342,17 +3346,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>수영구</t>
+          <t>연제구</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>19448</v>
+        <v>27572</v>
       </c>
     </row>
     <row r="142">
@@ -3363,17 +3367,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>연제구</t>
+          <t>영도구</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E142" t="n">
-        <v>27572</v>
+        <v>10633</v>
       </c>
     </row>
     <row r="143">
@@ -3384,17 +3388,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>영도구</t>
+          <t>중구</t>
         </is>
       </c>
       <c r="C143" t="n">
         <v>1</v>
       </c>
       <c r="D143" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E143" t="n">
-        <v>10633</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="144">
@@ -3405,38 +3409,34 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>중구</t>
+          <t>해운대구</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D144" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="E144" t="n">
-        <v>3368</v>
+        <v>52830</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>부산</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>해운대구</t>
-        </is>
-      </c>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>52</v>
+        <v>165</v>
       </c>
       <c r="E145" t="n">
-        <v>52830</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -3445,15 +3445,19 @@
           <t>서울</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>강남구</t>
+        </is>
+      </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D146" t="n">
-        <v>165</v>
+        <v>60</v>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>94062</v>
       </c>
     </row>
     <row r="147">
@@ -3464,17 +3468,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>강남구</t>
+          <t>강동구</t>
         </is>
       </c>
       <c r="C147" t="n">
         <v>3</v>
       </c>
       <c r="D147" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E147" t="n">
-        <v>94062</v>
+        <v>68859</v>
       </c>
     </row>
     <row r="148">
@@ -3485,17 +3489,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>강동구</t>
+          <t>강북구</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D148" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E148" t="n">
-        <v>68859</v>
+        <v>33445</v>
       </c>
     </row>
     <row r="149">
@@ -3506,17 +3510,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>강북구</t>
+          <t>강서구</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D149" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E149" t="n">
-        <v>33445</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="150">
@@ -3527,17 +3531,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>강서구</t>
+          <t>관악구</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D150" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E150" t="n">
-        <v>67200</v>
+        <v>57307</v>
       </c>
     </row>
     <row r="151">
@@ -3548,17 +3552,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>관악구</t>
+          <t>광진구</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E151" t="n">
-        <v>57307</v>
+        <v>44541</v>
       </c>
     </row>
     <row r="152">
@@ -3569,17 +3573,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>광진구</t>
+          <t>구로구</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D152" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E152" t="n">
-        <v>44541</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="153">
@@ -3590,17 +3594,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>구로구</t>
+          <t>금천구</t>
         </is>
       </c>
       <c r="C153" t="n">
         <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E153" t="n">
-        <v>45441</v>
+        <v>22192</v>
       </c>
     </row>
     <row r="154">
@@ -3611,17 +3615,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>금천구</t>
+          <t>노원구</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D154" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E154" t="n">
-        <v>22192</v>
+        <v>75253</v>
       </c>
     </row>
     <row r="155">
@@ -3632,17 +3636,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>노원구</t>
+          <t>도봉구</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D155" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E155" t="n">
-        <v>75253</v>
+        <v>36109</v>
       </c>
     </row>
     <row r="156">
@@ -3653,17 +3657,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>도봉구</t>
+          <t>동대문구</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E156" t="n">
-        <v>36109</v>
+        <v>49554</v>
       </c>
     </row>
     <row r="157">
@@ -3674,17 +3678,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>동대문구</t>
+          <t>동작구</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D157" t="n">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="E157" t="n">
-        <v>49554</v>
+        <v>49937</v>
       </c>
     </row>
     <row r="158">
@@ -3695,17 +3699,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>동작구</t>
+          <t>마포구</t>
         </is>
       </c>
       <c r="C158" t="n">
         <v>4</v>
       </c>
       <c r="D158" t="n">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="E158" t="n">
-        <v>49937</v>
+        <v>48563</v>
       </c>
     </row>
     <row r="159">
@@ -3716,17 +3720,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>마포구</t>
+          <t>서대문구</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D159" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E159" t="n">
-        <v>48563</v>
+        <v>42617</v>
       </c>
     </row>
     <row r="160">
@@ -3737,17 +3741,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>서대문구</t>
+          <t>서초구</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D160" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E160" t="n">
-        <v>42617</v>
+        <v>69878</v>
       </c>
     </row>
     <row r="161">
@@ -3758,17 +3762,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>서초구</t>
+          <t>성동구</t>
         </is>
       </c>
       <c r="C161" t="n">
         <v>2</v>
       </c>
       <c r="D161" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E161" t="n">
-        <v>69878</v>
+        <v>33719</v>
       </c>
     </row>
     <row r="162">
@@ -3779,17 +3783,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>성동구</t>
+          <t>성북구</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D162" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E162" t="n">
-        <v>33719</v>
+        <v>65974</v>
       </c>
     </row>
     <row r="163">
@@ -3800,17 +3804,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>성북구</t>
+          <t>송파구</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D163" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="E163" t="n">
-        <v>65974</v>
+        <v>91619</v>
       </c>
     </row>
     <row r="164">
@@ -3821,17 +3825,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>송파구</t>
+          <t>양천구</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D164" t="n">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="E164" t="n">
-        <v>91619</v>
+        <v>68798</v>
       </c>
     </row>
     <row r="165">
@@ -3842,17 +3846,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>양천구</t>
+          <t>영등포구</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D165" t="n">
-        <v>108</v>
+        <v>62</v>
       </c>
       <c r="E165" t="n">
-        <v>68798</v>
+        <v>40586</v>
       </c>
     </row>
     <row r="166">
@@ -3863,17 +3867,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>영등포구</t>
+          <t>용산구</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D166" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="E166" t="n">
-        <v>40586</v>
+        <v>23163</v>
       </c>
     </row>
     <row r="167">
@@ -3884,17 +3888,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>용산구</t>
+          <t>은평구</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D167" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E167" t="n">
-        <v>23163</v>
+        <v>56838</v>
       </c>
     </row>
     <row r="168">
@@ -3905,17 +3909,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>은평구</t>
+          <t>종로구</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D168" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="E168" t="n">
-        <v>56838</v>
+        <v>17655</v>
       </c>
     </row>
     <row r="169">
@@ -3926,17 +3930,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>종로구</t>
+          <t>중구</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D169" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E169" t="n">
-        <v>17655</v>
+        <v>12047</v>
       </c>
     </row>
     <row r="170">
@@ -3947,56 +3951,52 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>중구</t>
+          <t>중랑구</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D170" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E170" t="n">
-        <v>12047</v>
+        <v>41076</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>세종</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>중랑구</t>
+          <t>세종시</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D171" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E171" t="n">
-        <v>41076</v>
+        <v>153518</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>세종</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>세종시</t>
-        </is>
-      </c>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
       <c r="C172" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
@@ -4008,15 +4008,19 @@
           <t>울산</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>남구</t>
+        </is>
+      </c>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D173" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E173" t="n">
-        <v>0</v>
+        <v>43684</v>
       </c>
     </row>
     <row r="174">
@@ -4027,17 +4031,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>남구</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D174" t="n">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="E174" t="n">
-        <v>43684</v>
+        <v>23375</v>
       </c>
     </row>
     <row r="175">
@@ -4048,17 +4052,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="C175" t="n">
         <v>2</v>
       </c>
       <c r="D175" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E175" t="n">
-        <v>23375</v>
+        <v>36095</v>
       </c>
     </row>
     <row r="176">
@@ -4069,17 +4073,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>울주군</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D176" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E176" t="n">
-        <v>36095</v>
+        <v>31477</v>
       </c>
     </row>
     <row r="177">
@@ -4090,38 +4094,34 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>울주군</t>
+          <t>중구</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D177" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="E177" t="n">
-        <v>31477</v>
+        <v>27707</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>중구</t>
-        </is>
-      </c>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
       <c r="C178" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D178" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="E178" t="n">
-        <v>27707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -4130,15 +4130,19 @@
           <t>인천</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>강화군</t>
+        </is>
+      </c>
       <c r="C179" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D179" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E179" t="n">
-        <v>0</v>
+        <v>6431</v>
       </c>
     </row>
     <row r="180">
@@ -4149,17 +4153,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>강화군</t>
+          <t>계양구</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D180" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="E180" t="n">
-        <v>6431</v>
+        <v>34838</v>
       </c>
     </row>
     <row r="181">
@@ -4170,17 +4174,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>검단구</t>
+          <t>남동구</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D181" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E181" t="n">
-        <v>0</v>
+        <v>69529</v>
       </c>
     </row>
     <row r="182">
@@ -4191,17 +4195,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>계양구</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D182" t="n">
         <v>4</v>
       </c>
       <c r="E182" t="n">
-        <v>34838</v>
+        <v>6803</v>
       </c>
     </row>
     <row r="183">
@@ -4212,17 +4216,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>남동구</t>
+          <t>미추홀구</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E183" t="n">
-        <v>69529</v>
+        <v>56043</v>
       </c>
     </row>
     <row r="184">
@@ -4233,17 +4237,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>부평구</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D184" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="E184" t="n">
-        <v>6803</v>
+        <v>62015</v>
       </c>
     </row>
     <row r="185">
@@ -4254,17 +4258,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>미추홀구</t>
+          <t>서구</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="E185" t="n">
-        <v>56043</v>
+        <v>103185</v>
       </c>
     </row>
     <row r="186">
@@ -4275,17 +4279,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>부평구</t>
+          <t>연수구</t>
         </is>
       </c>
       <c r="C186" t="n">
         <v>2</v>
       </c>
       <c r="D186" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="E186" t="n">
-        <v>62015</v>
+        <v>71740</v>
       </c>
     </row>
     <row r="187">
@@ -4296,17 +4300,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>서구</t>
+          <t>옹진군</t>
         </is>
       </c>
       <c r="C187" t="n">
+        <v>2</v>
+      </c>
+      <c r="D187" t="n">
         <v>4</v>
       </c>
-      <c r="D187" t="n">
-        <v>15</v>
-      </c>
       <c r="E187" t="n">
-        <v>103185</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="188">
@@ -4317,122 +4321,118 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>서해구</t>
+          <t>중구</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D188" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
+        <v>25612</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>인천</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>연수구</t>
-        </is>
-      </c>
+          <t>전남광주</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
       <c r="C189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="E189" t="n">
-        <v>71740</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전남광주</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>영종구</t>
+          <t>강진군</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D190" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전남광주</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>옹진군</t>
+          <t>고흥군</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D191" t="n">
-        <v>4</v>
+        <v>160</v>
       </c>
       <c r="E191" t="n">
-        <v>1847</v>
+        <v>4664</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전남광주</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>제물포구</t>
+          <t>곡성군</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D192" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E192" t="n">
-        <v>0</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>전남광주</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>중구</t>
+          <t>광산구</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D193" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E193" t="n">
-        <v>25612</v>
+        <v>72609</v>
       </c>
     </row>
     <row r="194">
@@ -4441,15 +4441,19 @@
           <t>전남광주</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>광양시</t>
+        </is>
+      </c>
       <c r="C194" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D194" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E194" t="n">
-        <v>0</v>
+        <v>23555</v>
       </c>
     </row>
     <row r="195">
@@ -4460,17 +4464,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>강진군</t>
+          <t>구례군</t>
         </is>
       </c>
       <c r="C195" t="n">
         <v>2</v>
       </c>
       <c r="D195" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E195" t="n">
-        <v>3078</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="196">
@@ -4481,17 +4485,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>고흥군</t>
+          <t>나주시</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D196" t="n">
-        <v>160</v>
+        <v>4</v>
       </c>
       <c r="E196" t="n">
-        <v>4664</v>
+        <v>15649</v>
       </c>
     </row>
     <row r="197">
@@ -4502,17 +4506,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>곡성군</t>
+          <t>남구</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D197" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E197" t="n">
-        <v>2582</v>
+        <v>34554</v>
       </c>
     </row>
     <row r="198">
@@ -4523,17 +4527,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>광산구</t>
+          <t>담양군</t>
         </is>
       </c>
       <c r="C198" t="n">
         <v>4</v>
       </c>
       <c r="D198" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="E198" t="n">
-        <v>72609</v>
+        <v>4279</v>
       </c>
     </row>
     <row r="199">
@@ -4544,17 +4548,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>광양시</t>
+          <t>동구</t>
         </is>
       </c>
       <c r="C199" t="n">
         <v>3</v>
       </c>
       <c r="D199" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="E199" t="n">
-        <v>23555</v>
+        <v>14542</v>
       </c>
     </row>
     <row r="200">
@@ -4565,17 +4569,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>구례군</t>
+          <t>목포시</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D200" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="E200" t="n">
-        <v>2406</v>
+        <v>31815</v>
       </c>
     </row>
     <row r="201">
@@ -4586,17 +4590,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>나주시</t>
+          <t>무안군</t>
         </is>
       </c>
       <c r="C201" t="n">
         <v>2</v>
       </c>
       <c r="D201" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E201" t="n">
-        <v>15649</v>
+        <v>16175</v>
       </c>
     </row>
     <row r="202">
@@ -4607,17 +4611,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>남구</t>
+          <t>보성군</t>
         </is>
       </c>
       <c r="C202" t="n">
         <v>2</v>
       </c>
       <c r="D202" t="n">
-        <v>9</v>
+        <v>103</v>
       </c>
       <c r="E202" t="n">
-        <v>34554</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="203">
@@ -4628,17 +4632,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>담양군</t>
+          <t>북구</t>
         </is>
       </c>
       <c r="C203" t="n">
         <v>4</v>
       </c>
       <c r="D203" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E203" t="n">
-        <v>4279</v>
+        <v>64420</v>
       </c>
     </row>
     <row r="204">
@@ -4649,17 +4653,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>동구</t>
+          <t>서구</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D204" t="n">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="E204" t="n">
-        <v>14542</v>
+        <v>43390</v>
       </c>
     </row>
     <row r="205">
@@ -4670,17 +4674,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>목포시</t>
+          <t>순천시</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D205" t="n">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="E205" t="n">
-        <v>31815</v>
+        <v>43292</v>
       </c>
     </row>
     <row r="206">
@@ -4691,17 +4695,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>무안군</t>
+          <t>신안군</t>
         </is>
       </c>
       <c r="C206" t="n">
         <v>2</v>
       </c>
       <c r="D206" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="E206" t="n">
-        <v>16175</v>
+        <v>4287</v>
       </c>
     </row>
     <row r="207">
@@ -4712,17 +4716,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>보성군</t>
+          <t>여수시</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D207" t="n">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="E207" t="n">
-        <v>3405</v>
+        <v>36425</v>
       </c>
     </row>
     <row r="208">
@@ -4733,17 +4737,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>북구</t>
+          <t>영광군</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D208" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E208" t="n">
-        <v>64420</v>
+        <v>6127</v>
       </c>
     </row>
     <row r="209">
@@ -4754,17 +4758,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>서구</t>
+          <t>영암군</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D209" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="E209" t="n">
-        <v>43390</v>
+        <v>5792</v>
       </c>
     </row>
     <row r="210">
@@ -4775,17 +4779,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>순천시</t>
+          <t>완도군</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D210" t="n">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="E210" t="n">
-        <v>43292</v>
+        <v>4624</v>
       </c>
     </row>
     <row r="211">
@@ -4796,17 +4800,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>신안군</t>
+          <t>장성군</t>
         </is>
       </c>
       <c r="C211" t="n">
         <v>2</v>
       </c>
       <c r="D211" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="E211" t="n">
-        <v>4287</v>
+        <v>4728</v>
       </c>
     </row>
     <row r="212">
@@ -4817,17 +4821,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>여수시</t>
+          <t>장흥군</t>
         </is>
       </c>
       <c r="C212" t="n">
         <v>5</v>
       </c>
       <c r="D212" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E212" t="n">
-        <v>36425</v>
+        <v>3407</v>
       </c>
     </row>
     <row r="213">
@@ -4838,17 +4842,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>영광군</t>
+          <t>진도군</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D213" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E213" t="n">
-        <v>6127</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="214">
@@ -4859,17 +4863,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>영암군</t>
+          <t>함평군</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D214" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E214" t="n">
-        <v>5792</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="215">
@@ -4880,17 +4884,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>완도군</t>
+          <t>해남군</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D215" t="n">
-        <v>137</v>
+        <v>3</v>
       </c>
       <c r="E215" t="n">
-        <v>4624</v>
+        <v>6473</v>
       </c>
     </row>
     <row r="216">
@@ -4901,122 +4905,118 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>장성군</t>
+          <t>화순군</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D216" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E216" t="n">
-        <v>4728</v>
+        <v>7330</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>전남광주</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>장흥군</t>
-        </is>
-      </c>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
       <c r="C217" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="E217" t="n">
-        <v>3407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>전남광주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>진도군</t>
+          <t>고창군</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D218" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E218" t="n">
-        <v>2880</v>
+        <v>5501</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>전남광주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>함평군</t>
+          <t>군산시</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D219" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="E219" t="n">
-        <v>2617</v>
+        <v>37719</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>전남광주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>해남군</t>
+          <t>김제시</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D220" t="n">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="E220" t="n">
-        <v>6473</v>
+        <v>8722</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>전남광주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>화순군</t>
+          <t>남원시</t>
         </is>
       </c>
       <c r="C221" t="n">
         <v>3</v>
       </c>
       <c r="D221" t="n">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E221" t="n">
-        <v>7330</v>
+        <v>8838</v>
       </c>
     </row>
     <row r="222">
@@ -5025,15 +5025,19 @@
           <t>전북</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr"/>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>무주군</t>
+        </is>
+      </c>
       <c r="C222" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D222" t="n">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="E222" t="n">
-        <v>0</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="223">
@@ -5044,17 +5048,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>고창군</t>
+          <t>부안군</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D223" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="E223" t="n">
-        <v>5501</v>
+        <v>4749</v>
       </c>
     </row>
     <row r="224">
@@ -5065,17 +5069,17 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>군산시</t>
+          <t>순창군</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D224" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="E224" t="n">
-        <v>37719</v>
+        <v>3168</v>
       </c>
     </row>
     <row r="225">
@@ -5086,17 +5090,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>김제시</t>
+          <t>완주군</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D225" t="n">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="E225" t="n">
-        <v>8722</v>
+        <v>13100</v>
       </c>
     </row>
     <row r="226">
@@ -5107,17 +5111,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>남원시</t>
+          <t>익산시</t>
         </is>
       </c>
       <c r="C226" t="n">
         <v>3</v>
       </c>
       <c r="D226" t="n">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="E226" t="n">
-        <v>8838</v>
+        <v>39793</v>
       </c>
     </row>
     <row r="227">
@@ -5128,17 +5132,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>무주군</t>
+          <t>임실군</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D227" t="n">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="E227" t="n">
-        <v>2506</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="228">
@@ -5149,17 +5153,17 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>부안군</t>
+          <t>장수군</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D228" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="E228" t="n">
-        <v>4749</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="229">
@@ -5170,17 +5174,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>순창군</t>
+          <t>전주시 덕진구</t>
         </is>
       </c>
       <c r="C229" t="n">
         <v>3</v>
       </c>
       <c r="D229" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E229" t="n">
-        <v>3168</v>
+        <v>55545</v>
       </c>
     </row>
     <row r="230">
@@ -5191,17 +5195,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>완주군</t>
+          <t>전주시 완산구</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D230" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E230" t="n">
-        <v>13100</v>
+        <v>50456</v>
       </c>
     </row>
     <row r="231">
@@ -5212,17 +5216,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>익산시</t>
+          <t>정읍시</t>
         </is>
       </c>
       <c r="C231" t="n">
         <v>3</v>
       </c>
       <c r="D231" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E231" t="n">
-        <v>39793</v>
+        <v>12243</v>
       </c>
     </row>
     <row r="232">
@@ -5233,202 +5237,198 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>임실군</t>
+          <t>진안군</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D232" t="n">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="E232" t="n">
-        <v>2119</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>장수군</t>
-        </is>
-      </c>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
       <c r="C233" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="E233" t="n">
-        <v>2173</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>전주시</t>
+          <t>서귀포시</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D234" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="E234" t="n">
-        <v>0</v>
+        <v>25644</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>전주시 덕진구</t>
+          <t>제주시</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D235" t="n">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="E235" t="n">
-        <v>55545</v>
+        <v>79047</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>전주시 완산구</t>
-        </is>
-      </c>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
       <c r="C236" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D236" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="E236" t="n">
-        <v>50456</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>정읍시</t>
+          <t>계룡시</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D237" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E237" t="n">
-        <v>12243</v>
+        <v>8698</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>진안군</t>
+          <t>공주시</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D238" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="E238" t="n">
-        <v>2346</v>
+        <v>14122</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>제주</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr"/>
+          <t>충남</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>금산군</t>
+        </is>
+      </c>
       <c r="C239" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D239" t="n">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E239" t="n">
-        <v>0</v>
+        <v>5802</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>서귀포시</t>
+          <t>논산시</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D240" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="E240" t="n">
-        <v>25644</v>
+        <v>12435</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>충남</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>제주시</t>
+          <t>당진시</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D241" t="n">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="E241" t="n">
-        <v>79047</v>
+        <v>24114</v>
       </c>
     </row>
     <row r="242">
@@ -5437,15 +5437,19 @@
           <t>충남</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr"/>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>보령시</t>
+        </is>
+      </c>
       <c r="C242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D242" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E242" t="n">
-        <v>0</v>
+        <v>10457</v>
       </c>
     </row>
     <row r="243">
@@ -5456,17 +5460,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>계룡시</t>
+          <t>부여군</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D243" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E243" t="n">
-        <v>8698</v>
+        <v>5637</v>
       </c>
     </row>
     <row r="244">
@@ -5477,17 +5481,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>공주시</t>
+          <t>서산시</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D244" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="E244" t="n">
-        <v>14122</v>
+        <v>24373</v>
       </c>
     </row>
     <row r="245">
@@ -5498,17 +5502,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>금산군</t>
+          <t>서천군</t>
         </is>
       </c>
       <c r="C245" t="n">
         <v>3</v>
       </c>
       <c r="D245" t="n">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="E245" t="n">
-        <v>5802</v>
+        <v>4249</v>
       </c>
     </row>
     <row r="246">
@@ -5519,17 +5523,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>논산시</t>
+          <t>아산시</t>
         </is>
       </c>
       <c r="C246" t="n">
         <v>2</v>
       </c>
       <c r="D246" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E246" t="n">
-        <v>12435</v>
+        <v>61425</v>
       </c>
     </row>
     <row r="247">
@@ -5540,17 +5544,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>당진시</t>
+          <t>예산군</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D247" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E247" t="n">
-        <v>24114</v>
+        <v>8209</v>
       </c>
     </row>
     <row r="248">
@@ -5561,17 +5565,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>보령시</t>
+          <t>천안시</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D248" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="E248" t="n">
-        <v>10457</v>
+        <v>111587</v>
       </c>
     </row>
     <row r="249">
@@ -5582,17 +5586,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>부여군</t>
+          <t>천안시 동남구</t>
         </is>
       </c>
       <c r="C249" t="n">
         <v>4</v>
       </c>
       <c r="D249" t="n">
-        <v>55</v>
+        <v>182</v>
       </c>
       <c r="E249" t="n">
-        <v>5637</v>
+        <v>42367</v>
       </c>
     </row>
     <row r="250">
@@ -5603,17 +5607,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>서산시</t>
+          <t>천안시 서북구</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D250" t="n">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="E250" t="n">
-        <v>24373</v>
+        <v>69220</v>
       </c>
     </row>
     <row r="251">
@@ -5624,17 +5628,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>서천군</t>
+          <t>청양군</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D251" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E251" t="n">
-        <v>4249</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="252">
@@ -5645,17 +5649,17 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>아산시</t>
+          <t>태안군</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D252" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E252" t="n">
-        <v>61425</v>
+        <v>5599</v>
       </c>
     </row>
     <row r="253">
@@ -5666,143 +5670,139 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>예산군</t>
+          <t>홍성군</t>
         </is>
       </c>
       <c r="C253" t="n">
         <v>2</v>
       </c>
       <c r="D253" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E253" t="n">
-        <v>8209</v>
+        <v>14010</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>충남</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>천안시</t>
-        </is>
-      </c>
+          <t>충북</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
       <c r="C254" t="n">
         <v>0</v>
       </c>
       <c r="D254" t="n">
+        <v>205</v>
+      </c>
+      <c r="E254" t="n">
         <v>0</v>
-      </c>
-      <c r="E254" t="n">
-        <v>111587</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>천안시 동남구</t>
+          <t>괴산군</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D255" t="n">
-        <v>182</v>
+        <v>22</v>
       </c>
       <c r="E255" t="n">
-        <v>42367</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>천안시 서북구</t>
+          <t>단양군</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D256" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E256" t="n">
-        <v>69220</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>청양군</t>
+          <t>보은군</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D257" t="n">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="E257" t="n">
-        <v>3144</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>태안군</t>
+          <t>영동군</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D258" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="E258" t="n">
-        <v>5599</v>
+        <v>4206</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>충남</t>
+          <t>충북</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>홍성군</t>
+          <t>옥천군</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D259" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E259" t="n">
-        <v>14010</v>
+        <v>5489</v>
       </c>
     </row>
     <row r="260">
@@ -5811,15 +5811,19 @@
           <t>충북</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr"/>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>음성군</t>
+        </is>
+      </c>
       <c r="C260" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D260" t="n">
-        <v>205</v>
+        <v>26</v>
       </c>
       <c r="E260" t="n">
-        <v>0</v>
+        <v>11229</v>
       </c>
     </row>
     <row r="261">
@@ -5830,17 +5834,17 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>괴산군</t>
+          <t>제천시</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D261" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="E261" t="n">
-        <v>2890</v>
+        <v>18127</v>
       </c>
     </row>
     <row r="262">
@@ -5851,17 +5855,17 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>단양군</t>
+          <t>증평군</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D262" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E262" t="n">
-        <v>2306</v>
+        <v>5103</v>
       </c>
     </row>
     <row r="263">
@@ -5872,17 +5876,17 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>보은군</t>
+          <t>진천군</t>
         </is>
       </c>
       <c r="C263" t="n">
         <v>3</v>
       </c>
       <c r="D263" t="n">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="E263" t="n">
-        <v>2762</v>
+        <v>12184</v>
       </c>
     </row>
     <row r="264">
@@ -5893,17 +5897,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>영동군</t>
+          <t>청주시 상당구</t>
         </is>
       </c>
       <c r="C264" t="n">
         <v>2</v>
       </c>
       <c r="D264" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E264" t="n">
-        <v>4206</v>
+        <v>29547</v>
       </c>
     </row>
     <row r="265">
@@ -5914,17 +5918,17 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>옥천군</t>
+          <t>청주시 서원구</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D265" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E265" t="n">
-        <v>5489</v>
+        <v>30475</v>
       </c>
     </row>
     <row r="266">
@@ -5935,17 +5939,17 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>음성군</t>
+          <t>청주시 청원구</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D266" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E266" t="n">
-        <v>11229</v>
+        <v>31227</v>
       </c>
     </row>
     <row r="267">
@@ -5956,17 +5960,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>제천시</t>
+          <t>청주시 흥덕구</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D267" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="E267" t="n">
-        <v>18127</v>
+        <v>44532</v>
       </c>
     </row>
     <row r="268">
@@ -5977,142 +5981,16 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>증평군</t>
+          <t>충주시</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D268" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E268" t="n">
-        <v>5103</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>진천군</t>
-        </is>
-      </c>
-      <c r="C269" t="n">
-        <v>3</v>
-      </c>
-      <c r="D269" t="n">
-        <v>14</v>
-      </c>
-      <c r="E269" t="n">
-        <v>12184</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>청주시 상당구</t>
-        </is>
-      </c>
-      <c r="C270" t="n">
-        <v>2</v>
-      </c>
-      <c r="D270" t="n">
-        <v>16</v>
-      </c>
-      <c r="E270" t="n">
-        <v>29547</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>청주시 서원구</t>
-        </is>
-      </c>
-      <c r="C271" t="n">
-        <v>1</v>
-      </c>
-      <c r="D271" t="n">
-        <v>40</v>
-      </c>
-      <c r="E271" t="n">
-        <v>30475</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>청주시 청원구</t>
-        </is>
-      </c>
-      <c r="C272" t="n">
-        <v>1</v>
-      </c>
-      <c r="D272" t="n">
-        <v>6</v>
-      </c>
-      <c r="E272" t="n">
-        <v>31227</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>청주시 흥덕구</t>
-        </is>
-      </c>
-      <c r="C273" t="n">
-        <v>1</v>
-      </c>
-      <c r="D273" t="n">
-        <v>9</v>
-      </c>
-      <c r="E273" t="n">
-        <v>44532</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>충북</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>충주시</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>6</v>
-      </c>
-      <c r="D274" t="n">
-        <v>10</v>
-      </c>
-      <c r="E274" t="n">
         <v>27511</v>
       </c>
     </row>
